--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-tiflow-operation-outcome.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-tiflow-operation-outcome.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/tiflow-operation-outcome</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/tiflow-operation-outcome</t>
   </si>
   <si>
     <t>Version</t>
@@ -597,7 +597,7 @@
     <t>A human readable description of the error issue SHOULD be placed in details.text.</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/ValueSet/tiflow-operation-outcome-details-vs</t>
+    <t>https://gematik.de/fhir/tiflow/ValueSet/tiflow-operation-outcome-details-vs</t>
   </si>
   <si>
     <t>ERR-5</t>
@@ -1001,7 +1001,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="38.43359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.46875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.46484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
